--- a/account/resources/sample/iponeAreacodeConfig.xlsx
+++ b/account/resources/sample/iponeAreacodeConfig.xlsx
@@ -121,7 +121,7 @@
     <t>越南</t>
   </si>
   <si>
-    <t>087_092_05</t>
+    <t>87_92_5</t>
   </si>
 </sst>
 </file>
@@ -318,12 +318,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/account/resources/sample/iponeAreacodeConfig.xlsx
+++ b/account/resources/sample/iponeAreacodeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="iponeAreacodeConfig" sheetId="1" r:id="rId1"/>
@@ -78,12 +78,57 @@
         </r>
       </text>
     </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+服务端用
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+服务端用</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>序号ID</t>
   </si>
@@ -97,7 +142,10 @@
     <t>区号</t>
   </si>
   <si>
-    <t>需要屏蔽的号段</t>
+    <t>需要屏蔽的号段(手机前面几位数字)</t>
+  </si>
+  <si>
+    <t>首位电话号码屏蔽数字</t>
   </si>
   <si>
     <t>int</t>
@@ -106,6 +154,9 @@
     <t>list&lt;string&gt;{_}</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -118,10 +169,16 @@
     <t>blockedNumber</t>
   </si>
   <si>
+    <t>blockedFirstNumber</t>
+  </si>
+  <si>
     <t>越南</t>
   </si>
   <si>
     <t>87_92_5</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -134,7 +191,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +225,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
@@ -318,16 +383,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -344,85 +409,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,138 +720,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -802,13 +867,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1123,18 +1194,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
     <col min="2" max="4" width="17.7833333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="3"/>
+    <col min="5" max="5" width="33.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="23.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1147,47 +1218,58 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:6">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:5">
+    <row r="5" s="2" customFormat="1" spans="1:6">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1195,26 +1277,29 @@
         <v>14606</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>84</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:5">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+    <row r="6" s="3" customFormat="1" spans="1:6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+    <row r="7" spans="1:6">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/account/resources/sample/iponeAreacodeConfig.xlsx
+++ b/account/resources/sample/iponeAreacodeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="iponeAreacodeConfig" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>序号ID</t>
   </si>
@@ -179,6 +179,21 @@
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>印度</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>菲律宾</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>尼日利亚</t>
   </si>
 </sst>
 </file>
@@ -191,7 +206,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,7 +249,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color theme="0" tint="-0.35"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -720,138 +741,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -876,8 +897,17 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1194,8 +1224,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
     <col min="2" max="4" width="17.7833333333333" style="3" customWidth="1"/>
@@ -1285,21 +1315,116 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8">
+        <v>14601</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3">
+        <v>91</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8">
+        <v>14604</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8">
+        <v>14603</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8">
+        <v>14602</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8">
+        <v>14605</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" spans="1:6">
+      <c r="C13" s="9"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13"/>
+    </row>
+    <row r="14" ht="17.25" spans="1:6">
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" ht="17.25" spans="1:6">
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" ht="17.25" spans="1:6">
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16"/>
+    </row>
+    <row r="17" ht="17.25" spans="2:5">
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" ht="17.25" spans="2:5">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/account/resources/sample/iponeAreacodeConfig.xlsx
+++ b/account/resources/sample/iponeAreacodeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="iponeAreacodeConfig" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>序号ID</t>
   </si>
@@ -179,21 +179,6 @@
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>印度</t>
-  </si>
-  <si>
-    <t>巴西</t>
-  </si>
-  <si>
-    <t>菲律宾</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>尼日利亚</t>
   </si>
 </sst>
 </file>
@@ -206,7 +191,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,13 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -741,138 +720,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -897,17 +876,8 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1224,8 +1194,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
     <col min="2" max="4" width="17.7833333333333" style="3" customWidth="1"/>
@@ -1315,116 +1285,21 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:6">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8">
-        <v>14601</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3">
-        <v>91</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8">
-        <v>14604</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8">
-        <v>14603</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8">
-        <v>14602</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="8">
-        <v>14605</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" spans="1:6">
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13"/>
-    </row>
-    <row r="14" ht="17.25" spans="1:6">
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" ht="17.25" spans="1:6">
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" ht="17.25" spans="1:6">
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16"/>
-    </row>
-    <row r="17" ht="17.25" spans="2:5">
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18" ht="17.25" spans="2:5">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
